--- a/backend/templates/blendedlab.xlsx
+++ b/backend/templates/blendedlab.xlsx
@@ -403,7 +403,7 @@
     <numFmt numFmtId="166" formatCode="@"/>
     <numFmt numFmtId="167" formatCode="#,##0_ ;[RED]\-#,##0\ "/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="굴림체"/>
@@ -462,6 +462,13 @@
       <sz val="11"/>
       <name val="굴림체"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="20"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -644,7 +651,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -771,6 +778,10 @@
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="11" xfId="18" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1061,7 +1072,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="3"/>
@@ -1831,9 +1842,6 @@
     <mergeCell ref="B19:AF19"/>
     <mergeCell ref="B20:AF20"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="견적서"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="88" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1871,7 +1879,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="32" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="3"/>
@@ -2630,9 +2638,6 @@
     <mergeCell ref="B19:AF19"/>
     <mergeCell ref="B20:AF20"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="견적서"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="88" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
